--- a/tax/SanJose_expense.xlsx
+++ b/tax/SanJose_expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_Family\02_Tax\2026_taxform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50E1CBC-A25C-4356-A439-3D0F7FF218B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5329C88-B724-4437-8EB2-32F671C988D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1260" windowWidth="28800" windowHeight="14220" xr2:uid="{4306444B-0262-4BB7-ACAA-38E9B4FA6F9A}"/>
+    <workbookView xWindow="2370" yWindow="1140" windowWidth="29100" windowHeight="14220" xr2:uid="{4306444B-0262-4BB7-ACAA-38E9B4FA6F9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="16" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="36">
   <si>
     <t>Water</t>
   </si>
@@ -120,9 +120,6 @@
     <t>Dec</t>
   </si>
   <si>
-    <t xml:space="preserve">  Water Heater</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Roof</t>
   </si>
   <si>
@@ -132,7 +129,22 @@
     <t xml:space="preserve">  Electrical Panel</t>
   </si>
   <si>
-    <t xml:space="preserve">   Plumbing</t>
+    <t xml:space="preserve">  Unit B Paint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Unit B Washer and Dryer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Tree Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Basement Window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Unit D Plumbing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Unit C Plumbing</t>
   </si>
 </sst>
 </file>
@@ -513,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB7F9F73-8C34-4C98-A9F0-8B57D35360A3}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
@@ -619,103 +631,139 @@
       </c>
       <c r="B12" s="6">
         <f>SUM(Jan!B11, Feb!B11, Mar!B11, Apr!B11, May!B11, June!B11, July!B11, Aug!B11, Sep!B11, Oct!B11, Nov!B11, Dec!B11)</f>
-        <v>25452.81</v>
+        <v>25788.91</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2">
-        <f>SUM(Jan!B11, Feb!B11, Mar!B11, Apr!B11, May!B11)</f>
-        <v>4674.2299999999996</v>
+        <f>SUM(Jan!B11)</f>
+        <v>1734.21</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B14" s="2">
-        <f>SUM(June!B11, July!B11, Aug!B11, Sep!B11)</f>
-        <v>13916.859999999999</v>
+        <f>SUM(Feb!B11, Mar!B11, Apr!B11, May!B11)</f>
+        <v>2940.0199999999995</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2">
+        <f>SUM(June!B11, July!B11, Aug!B11)</f>
+        <v>12632.89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2">
         <f>SUM(Oct!B11, Nov!B11)</f>
         <v>4714.66</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="2">
-        <f>SUM(Dec!B11)</f>
-        <v>2147.06</v>
-      </c>
-    </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <f>SUM( Sep!B11)</f>
+        <v>1283.97</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="2">
+        <f>SUM(Dec!B11)</f>
+        <v>2483.1600000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B20" s="6">
         <f>SUM(Jan!B12, Feb!B12, Mar!B12, Apr!B12, May!B12, June!B12, July!B12, Aug!B12, Sep!B12, Oct!B12, Nov!B12, Dec!B12)</f>
         <v>26274.2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="6">
-        <f>SUM(Jan!B12, Feb!B12, Mar!B12, Apr!B12, May!B12)</f>
-        <v>1820</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="6">
-        <f>SUM(June!B12, July!B12, Aug!B12, Sep!B12)</f>
-        <v>21454.2</v>
-      </c>
-    </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B21" s="6">
+        <f>SUM( Aug!B12)</f>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="6">
+        <f>SUM(Jan!B12, Feb!B12, Apr!B12, May!B12)</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="6">
+        <f>SUM(June!B12, July!B12, Sep!B12)</f>
+        <v>20604.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="6">
+        <f>SUM(Mar!B12)</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="6">
         <f>SUM(Dec!B12)</f>
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="6"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="6"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B27" s="2">
         <f>SUM(Jan!B13, Feb!B13, Mar!B13, Apr!B13, May!B13, June!B13, July!B13, Aug!B13, Sep!B13, Oct!B13, Nov!B13, Dec!B13)</f>
         <v>2008.63</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B28" s="2">
         <f>SUM(Jan!B14, Feb!B14, Mar!B14, Apr!B14, May!B14, June!B14, July!B14, Aug!B14, Sep!B14, Oct!B14, Nov!B14, Dec!B14)</f>
         <v>2332.0300000000002</v>
       </c>
@@ -1214,8 +1262,8 @@
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>49.28+87.3+190.97+11.49+57.35+104.77+184.42+21.07+239.13+35.23+212.04+55.57+190.97+242.49+72.58+67.43+17.59+77.46+32.19+110.81+49.6+27.52+168.05+9.8-168.05</f>
-        <v>2147.06</v>
+        <f>49.28+87.3+190.97+11.49+57.35+104.77+184.42+21.07+239.13+35.23+212.04+55.57+190.97+242.49+72.58+67.43+17.59+77.46+32.19+110.81+49.6+27.52+168.05+9.8+168.05</f>
+        <v>2483.1600000000003</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">

--- a/tax/SanJose_expense.xlsx
+++ b/tax/SanJose_expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_Family\02_Tax\2026_taxform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5329C88-B724-4437-8EB2-32F671C988D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4310A5A0-C5EF-41F7-8F13-5A21053A51C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="1140" windowWidth="29100" windowHeight="14220" xr2:uid="{4306444B-0262-4BB7-ACAA-38E9B4FA6F9A}"/>
+    <workbookView xWindow="2850" yWindow="1680" windowWidth="29100" windowHeight="14220" xr2:uid="{4306444B-0262-4BB7-ACAA-38E9B4FA6F9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="16" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="37">
   <si>
     <t>Water</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t xml:space="preserve">  Unit C Plumbing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subtotal</t>
   </si>
 </sst>
 </file>
@@ -525,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB7F9F73-8C34-4C98-A9F0-8B57D35360A3}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
@@ -647,9 +650,9 @@
       <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="2">
-        <f>SUM(Feb!B11, Mar!B11, Apr!B11, May!B11)</f>
-        <v>2940.0199999999995</v>
+      <c r="B14" s="6">
+        <f>SUM(May!B11)</f>
+        <v>625.69999999999993</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -665,9 +668,9 @@
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="2">
-        <f>SUM(Oct!B11, Nov!B11)</f>
-        <v>4714.66</v>
+      <c r="B16" s="6">
+        <f>SUM(Feb!B11, Mar!B11, Apr!B11, Oct!B11, Nov!B11)</f>
+        <v>7028.9800000000005</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -689,87 +692,106 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="6">
+        <f>SUM(B13:B18)</f>
+        <v>25788.91</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B21" s="6">
         <f>SUM(Jan!B12, Feb!B12, Mar!B12, Apr!B12, May!B12, June!B12, July!B12, Aug!B12, Sep!B12, Oct!B12, Nov!B12, Dec!B12)</f>
         <v>26274.2</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B22" s="6">
         <f>SUM( Aug!B12)</f>
         <v>850</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B23" s="6">
         <f>SUM(Jan!B12, Feb!B12, Apr!B12, May!B12)</f>
         <v>320</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B24" s="6">
         <f>SUM(June!B12, July!B12, Sep!B12)</f>
         <v>20604.2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B25" s="6">
         <f>SUM(Mar!B12)</f>
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B26" s="6">
         <f>SUM(Dec!B12)</f>
         <v>3000</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="6"/>
-    </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="6">
+        <f>SUM(B22:B26)</f>
+        <v>26274.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="6"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B29" s="2">
         <f>SUM(Jan!B13, Feb!B13, Mar!B13, Apr!B13, May!B13, June!B13, July!B13, Aug!B13, Sep!B13, Oct!B13, Nov!B13, Dec!B13)</f>
         <v>2008.63</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B30" s="2">
         <f>SUM(Jan!B14, Feb!B14, Mar!B14, Apr!B14, May!B14, June!B14, July!B14, Aug!B14, Sep!B14, Oct!B14, Nov!B14, Dec!B14)</f>
         <v>2332.0300000000002</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1917,7 +1939,7 @@
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="6">
         <f>8.63+11+83.96+38.16+75.23+109.05+251.19+45.92+2.56</f>
         <v>625.69999999999993</v>
       </c>

--- a/tax/SanJose_expense.xlsx
+++ b/tax/SanJose_expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_Family\02_Tax\2026_taxform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4310A5A0-C5EF-41F7-8F13-5A21053A51C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772F7C6C-6FF7-4CED-9978-5EFF30D512E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="1680" windowWidth="29100" windowHeight="14220" xr2:uid="{4306444B-0262-4BB7-ACAA-38E9B4FA6F9A}"/>
+    <workbookView xWindow="795" yWindow="330" windowWidth="28800" windowHeight="14220" activeTab="12" xr2:uid="{4306444B-0262-4BB7-ACAA-38E9B4FA6F9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="16" r:id="rId1"/>
@@ -797,13 +797,13 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0062DDC1-E30E-418D-A088-C8B75004DBF3}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -811,7 +811,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -851,7 +851,7 @@
         <v>11.62</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -860,7 +860,7 @@
         <v>324.85000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -869,7 +869,7 @@
         <v>269.35000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -885,17 +885,100 @@
         <f>43.15+46.74+41.49+40.29+42.26+700+65.08+700</f>
         <v>1679.01</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>72.97+21.8+7.61+59.56+93.87+49.9+161.91+131.98+81.63+45.7+39.54+56+104.32+70.98+29.11+63.85+8.7+63.49+43.63+77.42</f>
+        <v>1283.97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>72.97+21.8+7.61+59.56+93.87+49.9+161.91+131.98+81.63+45.7+39.54+56+104.32+70.98+29.11+63.85+8.7+63.49+43.63+77.42</f>
+        <f>SUM(C11:AZ11)</f>
         <v>1283.97</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>72.97</f>
+        <v>72.97</v>
+      </c>
+      <c r="D11">
+        <f>21.8</f>
+        <v>21.8</v>
+      </c>
+      <c r="E11">
+        <f>7.61</f>
+        <v>7.61</v>
+      </c>
+      <c r="F11">
+        <f>59.56</f>
+        <v>59.56</v>
+      </c>
+      <c r="G11">
+        <f>93.87</f>
+        <v>93.87</v>
+      </c>
+      <c r="H11">
+        <f>49.9</f>
+        <v>49.9</v>
+      </c>
+      <c r="I11">
+        <f>161.91</f>
+        <v>161.91</v>
+      </c>
+      <c r="J11">
+        <f>131.98</f>
+        <v>131.97999999999999</v>
+      </c>
+      <c r="K11">
+        <f>81.63</f>
+        <v>81.63</v>
+      </c>
+      <c r="L11">
+        <f>45.7</f>
+        <v>45.7</v>
+      </c>
+      <c r="M11">
+        <f>39.54</f>
+        <v>39.54</v>
+      </c>
+      <c r="N11">
+        <f>56</f>
+        <v>56</v>
+      </c>
+      <c r="O11">
+        <f>104.32</f>
+        <v>104.32</v>
+      </c>
+      <c r="P11">
+        <f>70.98</f>
+        <v>70.98</v>
+      </c>
+      <c r="Q11">
+        <f>29.11</f>
+        <v>29.11</v>
+      </c>
+      <c r="R11">
+        <f>63.85</f>
+        <v>63.85</v>
+      </c>
+      <c r="S11">
+        <f>8.7</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="T11">
+        <f>63.49</f>
+        <v>63.49</v>
+      </c>
+      <c r="U11">
+        <f>43.63</f>
+        <v>43.63</v>
+      </c>
+      <c r="V11">
+        <v>77.42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -904,7 +987,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -912,7 +995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -929,13 +1012,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E92745-4D11-4B97-8A29-822EA5CD5505}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -943,7 +1026,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -951,7 +1034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -959,7 +1042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -967,7 +1050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -976,7 +1059,7 @@
         <v>599.85</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -984,7 +1067,7 @@
         <v>13.34</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -992,7 +1075,7 @@
         <v>155.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1001,7 +1084,7 @@
         <v>302.24</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1009,7 +1092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1017,17 +1100,168 @@
         <f>43.98+38.7+54.57+33.83+38.78+38.24+65+61.91</f>
         <v>375.01</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>14.16+4.5+26.08+89.63+108.89+4.5+18.46+52.22+26.08+2.99+12.78+70+61+28.17+71.93+14.15+106.31+39.29+78.1+45.75+37.92+178.19+6.5+79.02+3.67+83.64+46.31+94.06+110.6+119.23+199.17+109.04+50.31+93.33+75.11+60.11+100.33</f>
+        <v>2321.5300000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>14.16+4.5+26.08+89.63+108.89+4.5+18.46+52.22+26.08+2.99+12.78+70+61+28.17+71.93+14.15+106.31+39.29+78.1+45.75+37.92+178.19+6.5+79.02+3.67+83.64+46.31+94.06+110.6+119.23+199.17+109.04+50.31+93.33+75.11+60.11+100.33</f>
+        <f>SUM(C11:AZ11)</f>
         <v>2321.5300000000002</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>14.16</f>
+        <v>14.16</v>
+      </c>
+      <c r="D11">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="E11">
+        <f>26.08</f>
+        <v>26.08</v>
+      </c>
+      <c r="F11">
+        <f>89.63</f>
+        <v>89.63</v>
+      </c>
+      <c r="G11">
+        <f>108.89</f>
+        <v>108.89</v>
+      </c>
+      <c r="H11">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="I11">
+        <f>18.46</f>
+        <v>18.46</v>
+      </c>
+      <c r="J11">
+        <f>52.22</f>
+        <v>52.22</v>
+      </c>
+      <c r="K11">
+        <f>26.08</f>
+        <v>26.08</v>
+      </c>
+      <c r="L11">
+        <f>2.99</f>
+        <v>2.99</v>
+      </c>
+      <c r="M11">
+        <f>12.78</f>
+        <v>12.78</v>
+      </c>
+      <c r="N11">
+        <f>70</f>
+        <v>70</v>
+      </c>
+      <c r="O11">
+        <f>61</f>
+        <v>61</v>
+      </c>
+      <c r="P11">
+        <f>28.17</f>
+        <v>28.17</v>
+      </c>
+      <c r="Q11">
+        <f>71.93</f>
+        <v>71.930000000000007</v>
+      </c>
+      <c r="R11">
+        <f>14.15</f>
+        <v>14.15</v>
+      </c>
+      <c r="S11">
+        <f>106.31</f>
+        <v>106.31</v>
+      </c>
+      <c r="T11">
+        <f>39.29</f>
+        <v>39.29</v>
+      </c>
+      <c r="U11">
+        <f>78.1</f>
+        <v>78.099999999999994</v>
+      </c>
+      <c r="V11">
+        <f>45.75</f>
+        <v>45.75</v>
+      </c>
+      <c r="W11">
+        <f>37.92</f>
+        <v>37.92</v>
+      </c>
+      <c r="X11">
+        <f>178.19</f>
+        <v>178.19</v>
+      </c>
+      <c r="Y11">
+        <f>6.5</f>
+        <v>6.5</v>
+      </c>
+      <c r="Z11">
+        <f>79.02</f>
+        <v>79.02</v>
+      </c>
+      <c r="AA11">
+        <f>3.67</f>
+        <v>3.67</v>
+      </c>
+      <c r="AB11">
+        <f>83.64</f>
+        <v>83.64</v>
+      </c>
+      <c r="AC11">
+        <f>46.31</f>
+        <v>46.31</v>
+      </c>
+      <c r="AD11">
+        <f>94.06</f>
+        <v>94.06</v>
+      </c>
+      <c r="AE11">
+        <f>110.6</f>
+        <v>110.6</v>
+      </c>
+      <c r="AF11">
+        <f>119.23</f>
+        <v>119.23</v>
+      </c>
+      <c r="AG11">
+        <f>199.17</f>
+        <v>199.17</v>
+      </c>
+      <c r="AH11">
+        <f>109.04</f>
+        <v>109.04</v>
+      </c>
+      <c r="AI11">
+        <f>50.31</f>
+        <v>50.31</v>
+      </c>
+      <c r="AJ11">
+        <f>93.33</f>
+        <v>93.33</v>
+      </c>
+      <c r="AK11">
+        <f>75.11</f>
+        <v>75.11</v>
+      </c>
+      <c r="AL11">
+        <f>60.11</f>
+        <v>60.11</v>
+      </c>
+      <c r="AM11">
+        <v>100.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1035,7 +1269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1043,7 +1277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1060,13 +1294,13 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C88C9404-90F0-4C45-98BB-60AC959FBA35}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1074,7 +1308,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1082,7 +1316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1090,7 +1324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1098,7 +1332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1106,7 +1340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1114,7 +1348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1122,7 +1356,7 @@
         <v>155.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1131,7 +1365,7 @@
         <v>261.45</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1139,7 +1373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1147,17 +1381,96 @@
         <f>45.88+42.77+38.89+33.11+38.65+57.09</f>
         <v>256.39</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>14.7+50.09+14.82+65.48+24.29+24.09+18.74+184.42+50.77+193.48+923.92+36.29+20.64+53+198.18+28.21+184.42+79.02+228.57</f>
+        <v>2393.13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>14.7+50.09+14.82+65.48+24.29+24.09+18.74+184.42+50.77+193.48+923.92+36.29+20.64+53+198.18+28.21+184.42+79.02+228.57</f>
+        <f>SUM(C11:AZ11)</f>
         <v>2393.13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>14.7</f>
+        <v>14.7</v>
+      </c>
+      <c r="D11">
+        <f>50.09</f>
+        <v>50.09</v>
+      </c>
+      <c r="E11">
+        <f>14.82</f>
+        <v>14.82</v>
+      </c>
+      <c r="F11">
+        <f>65.48</f>
+        <v>65.48</v>
+      </c>
+      <c r="G11">
+        <f>24.29</f>
+        <v>24.29</v>
+      </c>
+      <c r="H11">
+        <f>24.09</f>
+        <v>24.09</v>
+      </c>
+      <c r="I11">
+        <f>18.74</f>
+        <v>18.739999999999998</v>
+      </c>
+      <c r="J11">
+        <f>184.42</f>
+        <v>184.42</v>
+      </c>
+      <c r="K11">
+        <f>50.77</f>
+        <v>50.77</v>
+      </c>
+      <c r="L11">
+        <f>193.48</f>
+        <v>193.48</v>
+      </c>
+      <c r="M11">
+        <f>923.92</f>
+        <v>923.92</v>
+      </c>
+      <c r="N11">
+        <f>36.29</f>
+        <v>36.29</v>
+      </c>
+      <c r="O11">
+        <f>20.64</f>
+        <v>20.64</v>
+      </c>
+      <c r="P11">
+        <f>53</f>
+        <v>53</v>
+      </c>
+      <c r="Q11">
+        <f>198.18</f>
+        <v>198.18</v>
+      </c>
+      <c r="R11">
+        <f>28.21</f>
+        <v>28.21</v>
+      </c>
+      <c r="S11">
+        <f>184.42</f>
+        <v>184.42</v>
+      </c>
+      <c r="T11">
+        <f>79.02</f>
+        <v>79.02</v>
+      </c>
+      <c r="U11">
+        <v>228.57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1165,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1173,7 +1486,7 @@
         <v>1039.24</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1190,13 +1503,13 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949DAC91-CCF9-473E-B12B-0F1930D2815D}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1204,7 +1517,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1212,7 +1525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1220,7 +1533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1228,7 +1541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1237,7 +1550,7 @@
         <v>747.67000000000007</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1245,7 +1558,7 @@
         <v>155.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1253,7 +1566,7 @@
         <v>155.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1262,7 +1575,7 @@
         <v>262.82</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1270,7 +1583,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1278,17 +1591,120 @@
         <f>36.51+35.08+80.2+33.19+270+33.95+41.3+26.07</f>
         <v>556.30000000000007</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>49.28+87.3+190.97+11.49+57.35+104.77+184.42+21.07+239.13+35.23+212.04+55.57+190.97+242.49+72.58+67.43+17.59+77.46+32.19+110.81+49.6+27.52+168.05+9.8+168.05</f>
+        <v>2483.1600000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>49.28+87.3+190.97+11.49+57.35+104.77+184.42+21.07+239.13+35.23+212.04+55.57+190.97+242.49+72.58+67.43+17.59+77.46+32.19+110.81+49.6+27.52+168.05+9.8+168.05</f>
+        <f>SUM(C11:AZ11)</f>
         <v>2483.1600000000003</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>49.28</f>
+        <v>49.28</v>
+      </c>
+      <c r="D11">
+        <f>87.3</f>
+        <v>87.3</v>
+      </c>
+      <c r="E11">
+        <f>190.97</f>
+        <v>190.97</v>
+      </c>
+      <c r="F11">
+        <f>11.49</f>
+        <v>11.49</v>
+      </c>
+      <c r="G11">
+        <f>57.35</f>
+        <v>57.35</v>
+      </c>
+      <c r="H11">
+        <f>104.77</f>
+        <v>104.77</v>
+      </c>
+      <c r="I11">
+        <f>184.42</f>
+        <v>184.42</v>
+      </c>
+      <c r="J11">
+        <f>21.07</f>
+        <v>21.07</v>
+      </c>
+      <c r="K11">
+        <f>239.13</f>
+        <v>239.13</v>
+      </c>
+      <c r="L11">
+        <f>35.23</f>
+        <v>35.229999999999997</v>
+      </c>
+      <c r="M11">
+        <f>212.04</f>
+        <v>212.04</v>
+      </c>
+      <c r="N11">
+        <f>55.57</f>
+        <v>55.57</v>
+      </c>
+      <c r="O11">
+        <f>190.97</f>
+        <v>190.97</v>
+      </c>
+      <c r="P11">
+        <f>242.49</f>
+        <v>242.49</v>
+      </c>
+      <c r="Q11">
+        <f>72.58</f>
+        <v>72.58</v>
+      </c>
+      <c r="R11">
+        <f>67.43</f>
+        <v>67.430000000000007</v>
+      </c>
+      <c r="S11">
+        <f>17.59</f>
+        <v>17.59</v>
+      </c>
+      <c r="T11">
+        <f>77.46</f>
+        <v>77.459999999999994</v>
+      </c>
+      <c r="U11">
+        <f>32.19</f>
+        <v>32.19</v>
+      </c>
+      <c r="V11">
+        <f>110.81</f>
+        <v>110.81</v>
+      </c>
+      <c r="W11">
+        <f>49.6</f>
+        <v>49.6</v>
+      </c>
+      <c r="X11">
+        <f>27.52</f>
+        <v>27.52</v>
+      </c>
+      <c r="Y11">
+        <f>168.05</f>
+        <v>168.05</v>
+      </c>
+      <c r="Z11">
+        <f>9.8</f>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AA11">
+        <v>168.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1297,7 +1713,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1305,7 +1721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1322,14 +1738,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23E9FE07-0FED-4064-9443-CA12CD81F35A}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1337,7 +1753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1345,7 +1761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1353,7 +1769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1361,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1369,7 +1785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1377,7 +1793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1385,7 +1801,7 @@
         <v>152.46</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1394,7 +1810,7 @@
         <v>345.34</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1402,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1410,17 +1826,33 @@
         <f>125.87+ 166.41</f>
         <v>292.27999999999997</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>1686.37 +17.42+6.5+23.92</f>
+        <v>1734.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>1686.37 + 17.42+6.5+23.92</f>
+        <f>SUM(C11:AZ11)</f>
         <v>1734.21</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>1686.37</v>
+      </c>
+      <c r="D11">
+        <v>17.420000000000002</v>
+      </c>
+      <c r="E11">
+        <v>6.5</v>
+      </c>
+      <c r="F11">
+        <v>23.92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1428,7 +1860,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1436,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1453,13 +1885,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE2B0D4-846E-4AA7-93F4-989EBC647507}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1467,7 +1899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1475,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1483,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1491,7 +1923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1500,7 +1932,7 @@
         <v>662.92</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1509,7 +1941,7 @@
         <v>17.79</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1517,7 +1949,7 @@
         <v>152.46</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1526,7 +1958,7 @@
         <v>278.33000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1534,7 +1966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1542,17 +1974,33 @@
         <f>51.23+31.44+39.5+40.35+43.54+36.95+36.31+56.56</f>
         <v>335.88</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>21.46+71.79+73.68+4.33</f>
+        <v>171.26000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>21.46+71.79+73.68+4.33</f>
+        <f>SUM(C11:AZ11)</f>
         <v>171.26000000000002</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>21.46</v>
+      </c>
+      <c r="D11">
+        <v>71.790000000000006</v>
+      </c>
+      <c r="E11">
+        <v>73.680000000000007</v>
+      </c>
+      <c r="F11">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1560,7 +2008,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1568,7 +2016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1585,13 +2033,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA3EE1E0-D3C7-4B80-9B53-8583EBDB6C81}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1599,7 +2047,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1607,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1615,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1623,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1631,7 +2079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1639,7 +2087,7 @@
         <v>15.53</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1647,7 +2095,7 @@
         <v>152.46</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1656,7 +2104,7 @@
         <v>278.32</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1664,7 +2112,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1672,17 +2120,30 @@
         <f>37.13+36.95+43.92+43.06+1400+38.2+66.7+40.02+65.71+56.3</f>
         <v>1827.99</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>10.89+7.57+5.42</f>
+        <v>23.880000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>10.89+7.57+5.42</f>
+        <f>SUM(C11:AZ11)</f>
         <v>23.880000000000003</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>10.89</v>
+      </c>
+      <c r="D11">
+        <v>7.57</v>
+      </c>
+      <c r="E11">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1690,7 +2151,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1698,7 +2159,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1715,13 +2176,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F936815-77C5-422B-A531-305720B087B7}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +2190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1737,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1745,7 +2206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1753,7 +2214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1762,7 +2223,7 @@
         <v>518.49</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1770,7 +2231,7 @@
         <v>13.14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1779,7 +2240,7 @@
         <v>270.07</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1788,7 +2249,7 @@
         <v>278.32</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1796,7 +2257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1804,17 +2265,59 @@
         <f>41.62+44.41+40.81+38</f>
         <v>164.84</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>47.93+43.62+288.04+1060.59+21.8+445.14+11.97+70.93+65.58+63.58</f>
+        <v>2119.1799999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>47.93+43.62+288.04+1060.59+21.8+445.14+11.97+70.93+65.58+63.58</f>
+        <f>SUM(C11:AZ11)</f>
         <v>2119.1799999999998</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>47.93</f>
+        <v>47.93</v>
+      </c>
+      <c r="D11">
+        <f>43.62</f>
+        <v>43.62</v>
+      </c>
+      <c r="E11">
+        <v>288.04000000000002</v>
+      </c>
+      <c r="F11">
+        <f>1060.59</f>
+        <v>1060.5899999999999</v>
+      </c>
+      <c r="G11">
+        <f>21.8</f>
+        <v>21.8</v>
+      </c>
+      <c r="H11">
+        <f>445.14</f>
+        <v>445.14</v>
+      </c>
+      <c r="I11">
+        <f>11.97</f>
+        <v>11.97</v>
+      </c>
+      <c r="J11">
+        <f>70.93</f>
+        <v>70.930000000000007</v>
+      </c>
+      <c r="K11">
+        <f>65.58</f>
+        <v>65.58</v>
+      </c>
+      <c r="L11">
+        <v>63.58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1822,7 +2325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1830,7 +2333,7 @@
         <v>244.39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1847,13 +2350,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F5CC7E9-6A9A-40D8-BB97-292449F94DEB}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1861,7 +2364,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1869,7 +2372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1877,7 +2380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1885,7 +2388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1893,7 +2396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1901,7 +2404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1909,7 +2412,7 @@
         <v>152.46</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1918,7 +2421,7 @@
         <v>269.35000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1926,7 +2429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1934,17 +2437,56 @@
         <f>60+75.2+39.36+21.66+42.37+44.02+42.62+45.92+68.52+67.89</f>
         <v>507.56</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>8.63+11+83.96+38.16+75.23+109.05+251.19+45.92+2.56</f>
+        <v>625.69999999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <f>8.63+11+83.96+38.16+75.23+109.05+251.19+45.92+2.56</f>
+        <f>SUM(C11:AZ11)</f>
         <v>625.69999999999993</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>8.63</f>
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="D11">
+        <f>11</f>
+        <v>11</v>
+      </c>
+      <c r="E11">
+        <f>83.96</f>
+        <v>83.96</v>
+      </c>
+      <c r="F11">
+        <f>38.16</f>
+        <v>38.159999999999997</v>
+      </c>
+      <c r="G11">
+        <f>75.23</f>
+        <v>75.23</v>
+      </c>
+      <c r="H11">
+        <f>109.05</f>
+        <v>109.05</v>
+      </c>
+      <c r="I11">
+        <f>251.19</f>
+        <v>251.19</v>
+      </c>
+      <c r="J11">
+        <f>45.92</f>
+        <v>45.92</v>
+      </c>
+      <c r="K11">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -1952,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1960,7 +2502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1977,13 +2519,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E44366-29F4-4D90-8240-9AA80D113C21}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1991,7 +2533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1999,7 +2541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -2007,7 +2549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -2015,7 +2557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -2024,7 +2566,7 @@
         <v>565.35</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -2032,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -2040,7 +2582,7 @@
         <v>152.46</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -2049,7 +2591,7 @@
         <v>270.39999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -2057,7 +2599,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -2065,17 +2607,60 @@
         <f>43.58+53.55+42.34+37.35+37.59+60.87+60.81+67.38</f>
         <v>403.46999999999997</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>3573.59+19.41+333.46+508.88+312.23+84.52+760.99+242.15+107.35+95.86</f>
+        <v>6038.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>3573.59+19.41+333.46+508.88+312.23+84.52+760.99+242.15+107.35+95.86</f>
+        <f>SUM(C11:AZ11)</f>
         <v>6038.44</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>3573.59</f>
+        <v>3573.59</v>
+      </c>
+      <c r="D11">
+        <f>19.41</f>
+        <v>19.41</v>
+      </c>
+      <c r="E11">
+        <f>333.46</f>
+        <v>333.46</v>
+      </c>
+      <c r="F11">
+        <f>508.88</f>
+        <v>508.88</v>
+      </c>
+      <c r="G11">
+        <f>312.23</f>
+        <v>312.23</v>
+      </c>
+      <c r="H11">
+        <f>84.52</f>
+        <v>84.52</v>
+      </c>
+      <c r="I11">
+        <f>760.99</f>
+        <v>760.99</v>
+      </c>
+      <c r="J11">
+        <f>242.15</f>
+        <v>242.15</v>
+      </c>
+      <c r="K11">
+        <f>107.35</f>
+        <v>107.35</v>
+      </c>
+      <c r="L11">
+        <v>95.86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -2084,7 +2669,7 @@
         <v>8948.4700000000012</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -2092,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -2109,13 +2694,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43FDF147-B31A-437C-8820-F7AD572752CA}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2123,7 +2708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -2131,7 +2716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -2139,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -2147,7 +2732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -2155,7 +2740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -2163,7 +2748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -2172,7 +2757,7 @@
         <v>545.93000000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -2181,7 +2766,7 @@
         <v>269.35000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -2189,7 +2774,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -2197,17 +2782,119 @@
         <f>43.41+27.53+35.33+38.34+43.28+48.64+47.4+49.03+52.19+77.46+59.05</f>
         <v>521.66</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>163.9+458.88+11.99+55.98+810.99+53.61+287.11+1228.65+150.22+140.77+40.04+83.94+14.16+285.37+103.59+44.48+34.33+56.66+19.63+19.6+17.23+29.41+48.31+67.3+105.9</f>
+        <v>4332.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>163.9+458.88+11.99+55.98+810.99+53.61+287.11+1228.65+150.22+140.77+40.04+83.94+14.16+285.37+103.59+44.48+34.33+56.66+19.63+19.6+17.23+29.41+48.31+67.3+105.9</f>
+        <f>SUM(C11:AZ11)</f>
         <v>4332.05</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>163.9</f>
+        <v>163.9</v>
+      </c>
+      <c r="D11">
+        <v>458.88</v>
+      </c>
+      <c r="E11">
+        <f>11.99</f>
+        <v>11.99</v>
+      </c>
+      <c r="F11">
+        <f>55.98</f>
+        <v>55.98</v>
+      </c>
+      <c r="G11">
+        <f>810.99</f>
+        <v>810.99</v>
+      </c>
+      <c r="H11">
+        <f>53.61</f>
+        <v>53.61</v>
+      </c>
+      <c r="I11">
+        <f>287.11</f>
+        <v>287.11</v>
+      </c>
+      <c r="J11">
+        <f>1228.65</f>
+        <v>1228.6500000000001</v>
+      </c>
+      <c r="K11">
+        <f>150.22</f>
+        <v>150.22</v>
+      </c>
+      <c r="L11">
+        <f>140.77</f>
+        <v>140.77000000000001</v>
+      </c>
+      <c r="M11">
+        <f>40.04</f>
+        <v>40.04</v>
+      </c>
+      <c r="N11">
+        <f>83.94</f>
+        <v>83.94</v>
+      </c>
+      <c r="O11">
+        <f>14.16</f>
+        <v>14.16</v>
+      </c>
+      <c r="P11">
+        <f>285.37</f>
+        <v>285.37</v>
+      </c>
+      <c r="Q11">
+        <f>103.59</f>
+        <v>103.59</v>
+      </c>
+      <c r="R11">
+        <f>44.48</f>
+        <v>44.48</v>
+      </c>
+      <c r="S11">
+        <f>34.33</f>
+        <v>34.33</v>
+      </c>
+      <c r="T11">
+        <f>56.66</f>
+        <v>56.66</v>
+      </c>
+      <c r="U11">
+        <f>19.63</f>
+        <v>19.63</v>
+      </c>
+      <c r="V11">
+        <f>19.6</f>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="W11">
+        <f>17.23</f>
+        <v>17.23</v>
+      </c>
+      <c r="X11">
+        <f>29.41</f>
+        <v>29.41</v>
+      </c>
+      <c r="Y11">
+        <f>48.31</f>
+        <v>48.31</v>
+      </c>
+      <c r="Z11">
+        <f>67.3</f>
+        <v>67.3</v>
+      </c>
+      <c r="AA11">
+        <v>105.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -2216,7 +2903,7 @@
         <v>10105.73</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -2224,7 +2911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -2241,13 +2928,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBEDB070-A42E-4BB2-ACF9-93FAC5F5F134}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2255,7 +2942,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -2263,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -2271,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -2279,7 +2966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -2288,7 +2975,7 @@
         <v>550.05999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -2296,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -2305,7 +2992,7 @@
         <v>179.46</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -2314,7 +3001,7 @@
         <v>269.35000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -2322,7 +3009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -2330,17 +3017,168 @@
         <f>37.66+42.97+40.55+40.01+36.15+20+39.24+800+40.68+55.83+59.51+53.6</f>
         <v>1266.1999999999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f>64.33+44.8+51.24+160.62+18.14+11.97+85.75+89.18+5.29+27.55+18.15+7.19+133.49+35.96+7.13+50.55+29.4+52.87+117.34+30.77+27.25+90.59+33.01+96.81+128.65+61.81+16.63+33.26+114.84+271.86+11.97+46.61+11.97+38.71+64.4+83.01+89.3</f>
+        <v>2262.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2">
-        <f>64.33+44.8+51.24+160.62+18.14+11.97+85.75+89.18+5.29+27.55+18.15+7.19+133.49+35.96+7.13+50.55+29.4+52.87+117.34+30.77+27.25+90.59+33.01+96.81+128.65+61.81+16.63+33.26+114.84+271.86+11.97+46.61+11.97+38.71+64.4+83.01+89.3</f>
+        <f>SUM(C11:AZ11)</f>
         <v>2262.4</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>64.33</f>
+        <v>64.33</v>
+      </c>
+      <c r="D11">
+        <f>44.8</f>
+        <v>44.8</v>
+      </c>
+      <c r="E11">
+        <f>51.24</f>
+        <v>51.24</v>
+      </c>
+      <c r="F11">
+        <f>160.62</f>
+        <v>160.62</v>
+      </c>
+      <c r="G11">
+        <f>18.14</f>
+        <v>18.14</v>
+      </c>
+      <c r="H11">
+        <f>11.97</f>
+        <v>11.97</v>
+      </c>
+      <c r="I11">
+        <f>85.75</f>
+        <v>85.75</v>
+      </c>
+      <c r="J11">
+        <f>89.18</f>
+        <v>89.18</v>
+      </c>
+      <c r="K11">
+        <f>5.29</f>
+        <v>5.29</v>
+      </c>
+      <c r="L11">
+        <f>27.55</f>
+        <v>27.55</v>
+      </c>
+      <c r="M11">
+        <f>18.15</f>
+        <v>18.149999999999999</v>
+      </c>
+      <c r="N11">
+        <f>7.19</f>
+        <v>7.19</v>
+      </c>
+      <c r="O11">
+        <f>133.49</f>
+        <v>133.49</v>
+      </c>
+      <c r="P11">
+        <f>35.96</f>
+        <v>35.96</v>
+      </c>
+      <c r="Q11">
+        <f>7.13</f>
+        <v>7.13</v>
+      </c>
+      <c r="R11">
+        <f>50.55</f>
+        <v>50.55</v>
+      </c>
+      <c r="S11">
+        <f>29.4</f>
+        <v>29.4</v>
+      </c>
+      <c r="T11">
+        <f>52.87</f>
+        <v>52.87</v>
+      </c>
+      <c r="U11">
+        <f>117.34</f>
+        <v>117.34</v>
+      </c>
+      <c r="V11">
+        <f>30.77</f>
+        <v>30.77</v>
+      </c>
+      <c r="W11">
+        <f>27.25</f>
+        <v>27.25</v>
+      </c>
+      <c r="X11">
+        <f>90.59</f>
+        <v>90.59</v>
+      </c>
+      <c r="Y11">
+        <f>33.01</f>
+        <v>33.01</v>
+      </c>
+      <c r="Z11">
+        <f>96.81</f>
+        <v>96.81</v>
+      </c>
+      <c r="AA11">
+        <f>128.65</f>
+        <v>128.65</v>
+      </c>
+      <c r="AB11">
+        <f>61.81</f>
+        <v>61.81</v>
+      </c>
+      <c r="AC11">
+        <f>16.63</f>
+        <v>16.63</v>
+      </c>
+      <c r="AD11">
+        <f>33.26</f>
+        <v>33.26</v>
+      </c>
+      <c r="AE11">
+        <f>114.84</f>
+        <v>114.84</v>
+      </c>
+      <c r="AF11">
+        <f>271.86</f>
+        <v>271.86</v>
+      </c>
+      <c r="AG11">
+        <f>11.97</f>
+        <v>11.97</v>
+      </c>
+      <c r="AH11">
+        <f>46.61</f>
+        <v>46.61</v>
+      </c>
+      <c r="AI11">
+        <f>11.97</f>
+        <v>11.97</v>
+      </c>
+      <c r="AJ11">
+        <f>38.71</f>
+        <v>38.71</v>
+      </c>
+      <c r="AK11">
+        <f>64.4</f>
+        <v>64.400000000000006</v>
+      </c>
+      <c r="AL11">
+        <f>83.01</f>
+        <v>83.01</v>
+      </c>
+      <c r="AM11">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -2349,7 +3187,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -2357,7 +3195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
